--- a/data/trans_orig/P70C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023</t>
+          <t>Población según si le es dificil cumplir con las obligaciones familiares debido al tiempo que paso en el trabajo en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137904</t>
+          <t>139051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178317</t>
+          <t>178763</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112421</t>
+          <t>112181</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140709</t>
+          <t>140030</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>262173</t>
+          <t>260680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310627</t>
+          <t>309977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,82%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61323</t>
+          <t>61769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91625</t>
+          <t>92202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55302</t>
+          <t>55525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78023</t>
+          <t>78453</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123044</t>
+          <t>122365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>158975</t>
+          <t>162667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19785</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43596</t>
+          <t>43150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14615</t>
+          <t>14407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29140</t>
+          <t>29634</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39072</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68011</t>
+          <t>66868</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26079</t>
+          <t>26167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51655</t>
+          <t>49183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>10921</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>42616</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68750</t>
+          <t>69247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13940</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>32262</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62126</t>
+          <t>60645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>352978</t>
+          <t>355919</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669378</t>
+          <t>675725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>165924</t>
+          <t>161552</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>201013</t>
+          <t>198080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>535271</t>
+          <t>534485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>960262</t>
+          <t>915575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>75,72%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61691</t>
+          <t>56607</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>206200</t>
+          <t>204254</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95221</t>
+          <t>96061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>125717</t>
+          <t>127828</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>118512</t>
+          <t>129021</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>317133</t>
+          <t>319853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22371</t>
+          <t>23928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94815</t>
+          <t>93772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>24072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>42764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45666</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123514</t>
+          <t>125167</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25055</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97599</t>
+          <t>98084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>37991</t>
+          <t>36759</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61307</t>
+          <t>59927</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50549</t>
+          <t>60105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>144172</t>
+          <t>148193</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53880</t>
+          <t>55106</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>31216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77517</t>
+          <t>77457</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33033</t>
+          <t>35049</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13268</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42337</t>
+          <t>42559</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186432</t>
+          <t>188388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>228198</t>
+          <t>229294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161173</t>
+          <t>161037</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>231089</t>
+          <t>232525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>365047</t>
+          <t>359715</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>440568</t>
+          <t>440353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50621</t>
+          <t>50311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85283</t>
+          <t>83994</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34257</t>
+          <t>32867</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65716</t>
+          <t>65596</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93629</t>
+          <t>93392</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140182</t>
+          <t>140988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15134</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>39796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34094</t>
+          <t>33427</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>36108</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63438</t>
+          <t>67059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57797</t>
+          <t>57127</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>19973</t>
+          <t>20233</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>41632</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53023</t>
+          <t>54218</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>89607</t>
+          <t>93136</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>16379</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34585</t>
+          <t>35234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>22941</t>
+          <t>23459</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44312</t>
+          <t>44603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18328</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>31734</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>219044</t>
+          <t>218732</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>263078</t>
+          <t>264163</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240272</t>
+          <t>240957</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>356571</t>
+          <t>355827</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>477938</t>
+          <t>476100</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>616385</t>
+          <t>623015</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,52%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>106996</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>146713</t>
+          <t>146063</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55239</t>
+          <t>52668</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>112480</t>
+          <t>111679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>169961</t>
+          <t>170252</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>245722</t>
+          <t>246633</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25165</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48865</t>
+          <t>47857</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20059</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>47459</t>
+          <t>46840</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51186</t>
+          <t>52035</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>88212</t>
+          <t>88677</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19205</t>
+          <t>18936</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>39856</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40470</t>
+          <t>39681</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41427</t>
+          <t>41412</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72495</t>
+          <t>72370</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17855</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40861</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37513</t>
+          <t>37804</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>39503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68914</t>
+          <t>70862</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>38564</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20171</t>
+          <t>20752</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>51370</t>
+          <t>50404</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>973435</t>
+          <t>968866</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1360166</t>
+          <t>1379152</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>714590</t>
+          <t>721708</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>885552</t>
+          <t>883061</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1730046</t>
+          <t>1735249</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2220712</t>
+          <t>2259673</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>273837</t>
+          <t>265924</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>470372</t>
+          <t>473770</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>263452</t>
+          <t>269935</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>352211</t>
+          <t>349112</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>562213</t>
+          <t>559840</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>801082</t>
+          <t>796708</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>97524</t>
+          <t>97858</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>183324</t>
+          <t>185073</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>93200</t>
+          <t>91080</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>133419</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>202450</t>
+          <t>204806</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>300691</t>
+          <t>302277</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>115533</t>
+          <t>112826</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>203532</t>
+          <t>204619</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>101871</t>
+          <t>99311</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>146653</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>230262</t>
+          <t>228472</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>331668</t>
+          <t>334671</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>58064</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>116220</t>
+          <t>119010</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>114303</t>
+          <t>112522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>144085</t>
+          <t>146876</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>218736</t>
+          <t>216496</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31410</t>
+          <t>31632</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>69061</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>63149</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,47 +4525,47 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
+          <t>2,03%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>4,32%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>90205</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>66438</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>116558</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>90205</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>66396</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>118320</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>1,94%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P70C2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P70C2_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>158503</t>
+          <t>181528</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139051</t>
+          <t>159439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>178763</t>
+          <t>204334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>126916</t>
+          <t>141021</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112181</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>140030</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>285419</t>
+          <t>322549</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>260680</t>
+          <t>295468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>309977</t>
+          <t>347263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>54,11%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>74866</t>
+          <t>82003</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61769</t>
+          <t>66539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92202</t>
+          <t>99730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66147</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55525</t>
+          <t>57762</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78453</t>
+          <t>82554</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>141013</t>
+          <t>151879</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122365</t>
+          <t>132965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162667</t>
+          <t>171592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29214</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19307</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43150</t>
+          <t>47361</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14407</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29634</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>50367</t>
+          <t>52805</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>41427</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66868</t>
+          <t>71884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37169</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26167</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>52340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16733</t>
+          <t>17277</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>25022</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>53903</t>
+          <t>55121</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42616</t>
+          <t>41973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69247</t>
+          <t>70740</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23708</t>
+          <t>24931</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37541</t>
+          <t>38517</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13362</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>36022</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>47563</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32262</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60645</t>
+          <t>68160</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14640</t>
+          <t>16030</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>7558</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>11853</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6829</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>19729</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>332057</t>
+          <t>365736</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>332057</t>
+          <t>365736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>332057</t>
+          <t>365736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>254747</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>254747</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254747</t>
+          <t>276032</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>586805</t>
+          <t>641768</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>586805</t>
+          <t>641768</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>586805</t>
+          <t>641768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>501613</t>
+          <t>292129</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>355919</t>
+          <t>264393</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>675725</t>
+          <t>322345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181579</t>
+          <t>203203</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>161552</t>
+          <t>183365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>198080</t>
+          <t>221655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>683192</t>
+          <t>495333</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>534485</t>
+          <t>462592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>915575</t>
+          <t>530602</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133443</t>
+          <t>150249</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56607</t>
+          <t>126461</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>204254</t>
+          <t>174626</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110328</t>
+          <t>122097</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>96061</t>
+          <t>106414</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>127828</t>
+          <t>139946</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>243771</t>
+          <t>272345</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129021</t>
+          <t>243982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319853</t>
+          <t>301159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>58017</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23928</t>
+          <t>47267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>93772</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24072</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>98113</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>79602</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125167</t>
+          <t>119965</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>61351</t>
+          <t>68084</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>51833</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>98084</t>
+          <t>89812</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>48050</t>
+          <t>53212</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>41834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59927</t>
+          <t>67546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>109401</t>
+          <t>121296</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60105</t>
+          <t>99535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>148193</t>
+          <t>144880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>34135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>23142</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>55106</t>
+          <t>50642</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15693</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>36949</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55044</t>
+          <t>60162</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>45896</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>77084</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>19099</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27013</t>
+          <t>31984</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>22386</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>44597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2198,17 +2198,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>806332</t>
+          <t>628627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402825</t>
+          <t>450606</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1209157</t>
+          <t>1079233</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>208397</t>
+          <t>242069</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>188388</t>
+          <t>218405</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>229294</t>
+          <t>264890</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>184375</t>
+          <t>178352</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>161037</t>
+          <t>161236</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>232525</t>
+          <t>195913</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>392771</t>
+          <t>420422</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359715</t>
+          <t>391276</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>440353</t>
+          <t>448185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>58,88%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>65268</t>
+          <t>81631</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>50311</t>
+          <t>64171</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>83994</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51575</t>
+          <t>63668</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32867</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65596</t>
+          <t>77553</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>116843</t>
+          <t>145299</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93392</t>
+          <t>123273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>140988</t>
+          <t>167973</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24231</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15522</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39796</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>27095</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>37471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>48448</t>
+          <t>53248</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>40283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>67059</t>
+          <t>69971</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40202</t>
+          <t>46162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>26523</t>
+          <t>31932</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>57127</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>30400</t>
+          <t>34068</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>25497</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41632</t>
+          <t>45060</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>70602</t>
+          <t>80230</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54218</t>
+          <t>63438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>100421</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>12732</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>23008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,27 +2802,27 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23518</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>36887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>27872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>44603</t>
+          <t>51206</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>12851</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>10419</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31734</t>
+          <t>35700</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2993,17 +2993,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357368</t>
+          <t>421597</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>324504</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>681872</t>
+          <t>761199</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>241007</t>
+          <t>260413</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>218732</t>
+          <t>235274</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>264163</t>
+          <t>283802</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>281194</t>
+          <t>229713</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>240957</t>
+          <t>211788</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>355827</t>
+          <t>247646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>522202</t>
+          <t>490126</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>476100</t>
+          <t>458935</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>623015</t>
+          <t>519028</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>53,82%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>126022</t>
+          <t>137092</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>105867</t>
+          <t>117388</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>146063</t>
+          <t>160093</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>98366</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>84011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>111679</t>
+          <t>112879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>216025</t>
+          <t>235458</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>170252</t>
+          <t>211318</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>246633</t>
+          <t>261421</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>47857</t>
+          <t>61265</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>35057</t>
+          <t>40462</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21455</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>46840</t>
+          <t>51392</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>70668</t>
+          <t>85597</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>69734</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>88677</t>
+          <t>107859</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>28988</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39856</t>
+          <t>40110</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>42868</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>57275</t>
+          <t>61427</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41412</t>
+          <t>47386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>72370</t>
+          <t>75849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -3562,32 +3562,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27036</t>
+          <t>27796</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>40403</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>30903</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>37804</t>
+          <t>40373</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>53916</t>
+          <t>58699</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>39503</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70862</t>
+          <t>74071</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>16004</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21636</t>
+          <t>26562</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>17043</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10128</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>38564</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>30767</t>
+          <t>33048</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20752</t>
+          <t>23116</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50404</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>469995</t>
+          <t>515428</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>469995</t>
+          <t>515428</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>469995</t>
+          <t>515428</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>480858</t>
+          <t>448926</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>950853</t>
+          <t>964354</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>950853</t>
+          <t>964354</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>950853</t>
+          <t>964354</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1109519</t>
+          <t>976139</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>968866</t>
+          <t>927042</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1379152</t>
+          <t>1021654</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>774064</t>
+          <t>752290</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>721708</t>
+          <t>715871</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>883061</t>
+          <t>789502</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1883584</t>
+          <t>1728429</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1735249</t>
+          <t>1668072</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2259673</t>
+          <t>1789019</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>51,91%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>399600</t>
+          <t>450975</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>265924</t>
+          <t>412655</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>473770</t>
+          <t>497366</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318053</t>
+          <t>354006</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>269935</t>
+          <t>323512</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>349112</t>
+          <t>382697</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>717653</t>
+          <t>804981</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>559840</t>
+          <t>757316</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>796708</t>
+          <t>857776</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>147073</t>
+          <t>163774</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>97858</t>
+          <t>135920</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>185073</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>113146</t>
+          <t>125988</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>91080</t>
+          <t>108817</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>130862</t>
+          <t>145936</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>260219</t>
+          <t>289762</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>204806</t>
+          <t>258054</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>302277</t>
+          <t>326101</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>166908</t>
+          <t>181078</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>112826</t>
+          <t>155075</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>204619</t>
+          <t>213610</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>124273</t>
+          <t>136996</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>99311</t>
+          <t>118215</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>146653</t>
+          <t>157072</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>291181</t>
+          <t>318074</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>228472</t>
+          <t>286651</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>334671</t>
+          <t>356925</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>99594</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>61214</t>
+          <t>80100</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>119010</t>
+          <t>124873</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>93416</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>86200</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>125254</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>185845</t>
+          <t>204951</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>146876</t>
+          <t>176572</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>216496</t>
+          <t>232658</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>50223</t>
+          <t>59829</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>69061</t>
+          <t>78461</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>39982</t>
+          <t>40529</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>29934</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>63149</t>
+          <t>52355</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>90205</t>
+          <t>100357</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>82215</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>116558</t>
+          <t>125061</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4583,17 +4583,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1965751</t>
+          <t>1931388</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4618,17 +4618,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1462935</t>
+          <t>1515166</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3428686</t>
+          <t>3446554</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
